--- a/research/traditional_assets/database/data/france/france_financial_svcs_non_bank_insurance.xlsx
+++ b/research/traditional_assets/database/data/france/france_financial_svcs_non_bank_insurance.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ5"/>
+  <dimension ref="A1:AQ4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,121 +588,115 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0002500000000000002</v>
+        <v>0.0574</v>
       </c>
       <c r="E2">
-        <v>-0.029</v>
+        <v>0.0271</v>
       </c>
       <c r="G2">
-        <v>0.01540226826753584</v>
+        <v>0.01257321598331749</v>
       </c>
       <c r="H2">
-        <v>0.01540226826753584</v>
+        <v>0.01257321598331749</v>
       </c>
       <c r="I2">
-        <v>0.01247189939322832</v>
+        <v>0.01039663306890468</v>
       </c>
       <c r="J2">
-        <v>0.01152569116031462</v>
+        <v>0.008724913898763158</v>
       </c>
       <c r="K2">
-        <v>557.75</v>
+        <v>727.5</v>
       </c>
       <c r="L2">
-        <v>0.1855023780224166</v>
+        <v>0.2230979177527676</v>
       </c>
       <c r="M2">
-        <v>134</v>
+        <v>254.1</v>
       </c>
       <c r="N2">
-        <v>0.03416449951557799</v>
+        <v>0.07555304471931494</v>
       </c>
       <c r="O2">
-        <v>0.2402510085163604</v>
+        <v>0.349278350515464</v>
       </c>
       <c r="P2">
-        <v>96</v>
+        <v>254.1</v>
       </c>
       <c r="Q2">
-        <v>0.02447605935444393</v>
+        <v>0.07555304471931494</v>
       </c>
       <c r="R2">
-        <v>0.1721201255042582</v>
+        <v>0.349278350515464</v>
       </c>
       <c r="S2">
-        <v>37.99999999999999</v>
+        <v>0</v>
       </c>
       <c r="T2">
-        <v>0.2835820895522387</v>
+        <v>0</v>
       </c>
       <c r="U2">
-        <v>5798.360000000001</v>
+        <v>5346.8</v>
       </c>
       <c r="V2">
-        <v>1.478343786650349</v>
+        <v>1.589795432921028</v>
       </c>
       <c r="W2">
-        <v>0.1765039727582293</v>
+        <v>0.1886491135024315</v>
       </c>
       <c r="X2">
-        <v>0.02566312641861677</v>
+        <v>0.05103199746182066</v>
       </c>
       <c r="Y2">
-        <v>0.1508408463396125</v>
+        <v>0.1376171160406109</v>
       </c>
       <c r="Z2">
-        <v>-2.813256806105891</v>
-      </c>
-      <c r="AA2">
-        <v>0.1905460771723843</v>
+        <v>21.92924055655309</v>
       </c>
       <c r="AB2">
-        <v>0.02450662698373873</v>
-      </c>
-      <c r="AC2">
-        <v>0.1666414176330165</v>
+        <v>0.04927074513820548</v>
       </c>
       <c r="AD2">
-        <v>965.301</v>
+        <v>1113.02</v>
       </c>
       <c r="AE2">
-        <v>0.5187004719021281</v>
+        <v>0.8230961280435625</v>
       </c>
       <c r="AF2">
-        <v>965.8197004719021</v>
+        <v>1113.843096128043</v>
       </c>
       <c r="AG2">
-        <v>-4832.540299528098</v>
+        <v>-4232.956903871956</v>
       </c>
       <c r="AH2">
-        <v>0.1975891587299984</v>
+        <v>0.2487898982011916</v>
       </c>
       <c r="AI2">
-        <v>0.2019267661340831</v>
+        <v>0.2197083847931514</v>
       </c>
       <c r="AJ2">
-        <v>5.30849870321372</v>
+        <v>4.866827598640279</v>
       </c>
       <c r="AK2">
-        <v>4.759527718710787</v>
+        <v>15.27278175191167</v>
       </c>
       <c r="AL2">
-        <v>2.955</v>
+        <v>0.044</v>
       </c>
       <c r="AM2">
-        <v>2.798</v>
+        <v>0.044</v>
       </c>
       <c r="AN2">
-        <v>25.9259527838208</v>
+        <v>32.01369114390083</v>
       </c>
       <c r="AO2">
-        <v>12.54483925549915</v>
+        <v>754.5454545454546</v>
       </c>
       <c r="AP2">
-        <v>-129.7918593593881</v>
+        <v>-121.7521472624028</v>
       </c>
       <c r="AQ2">
-        <v>13.24874910650465</v>
+        <v>754.5454545454546</v>
       </c>
     </row>
     <row r="3">
@@ -713,7 +707,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Advenis SA (ENXTPA:ADV)</t>
+          <t>Rothschild &amp; Co SCA (ENXTPA:ROTH)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -721,116 +715,101 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D3">
-        <v>-0.0194</v>
-      </c>
       <c r="G3">
-        <v>0.02539109506618532</v>
+        <v>0</v>
       </c>
       <c r="H3">
-        <v>0.02539109506618532</v>
+        <v>0</v>
       </c>
       <c r="I3">
-        <v>0.02731648616125151</v>
+        <v>0.0002196656057517709</v>
       </c>
       <c r="J3">
-        <v>0.02731648616125151</v>
+        <v>0.0001785557411154709</v>
       </c>
       <c r="K3">
-        <v>-2.85</v>
+        <v>698.8</v>
       </c>
       <c r="L3">
-        <v>-0.03429602888086643</v>
+        <v>0.2185457388584832</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>231.8</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.07840882183810845</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>0.3317115054378936</v>
       </c>
       <c r="P3">
-        <v>-0</v>
+        <v>231.8</v>
       </c>
       <c r="Q3">
-        <v>-0</v>
+        <v>0.07840882183810845</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>0.3317115054378936</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
       <c r="U3">
-        <v>6.66</v>
+        <v>5330.5</v>
       </c>
       <c r="V3">
-        <v>0.1644444444444444</v>
+        <v>1.803098467679193</v>
       </c>
       <c r="W3">
-        <v>-0.9468438538205981</v>
+        <v>0.221658313772759</v>
       </c>
       <c r="X3">
-        <v>0.0300335367887186</v>
+        <v>0.05248357751264067</v>
       </c>
       <c r="Y3">
-        <v>-0.9768773906093167</v>
-      </c>
-      <c r="Z3">
-        <v>14.35233160621762</v>
-      </c>
-      <c r="AA3">
-        <v>0.3920552677029361</v>
+        <v>0.1691747362601183</v>
       </c>
       <c r="AB3">
-        <v>0.02801978764901685</v>
-      </c>
-      <c r="AC3">
-        <v>0.3640354800539193</v>
+        <v>0.0490800634227568</v>
       </c>
       <c r="AD3">
-        <v>38.4</v>
+        <v>1107.9</v>
       </c>
       <c r="AE3">
-        <v>0</v>
+        <v>0.8230961280435625</v>
       </c>
       <c r="AF3">
-        <v>38.4</v>
+        <v>1108.723096128044</v>
       </c>
       <c r="AG3">
-        <v>31.74</v>
+        <v>-4221.776903871956</v>
       </c>
       <c r="AH3">
-        <v>0.4866920152091254</v>
+        <v>0.2727470594654451</v>
       </c>
       <c r="AI3">
-        <v>0.7097966728280962</v>
+        <v>0.2264168164467121</v>
       </c>
       <c r="AJ3">
-        <v>0.4393687707641196</v>
+        <v>3.336115334033094</v>
       </c>
       <c r="AK3">
-        <v>0.6690556492411467</v>
+        <v>9.73484376543705</v>
       </c>
       <c r="AL3">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="AM3">
-        <v>2.773</v>
+        <v>0</v>
       </c>
       <c r="AN3">
-        <v>34.90909090909091</v>
-      </c>
-      <c r="AO3">
-        <v>0.7747440273037542</v>
+        <v>1277.854671280277</v>
       </c>
       <c r="AP3">
-        <v>28.85454545454545</v>
-      </c>
-      <c r="AQ3">
-        <v>0.8186080057699242</v>
+        <v>-4869.40819362394</v>
       </c>
     </row>
     <row r="4">
@@ -850,46 +829,46 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0199</v>
+        <v>0.0574</v>
       </c>
       <c r="E4">
-        <v>-0.029</v>
+        <v>0.0271</v>
       </c>
       <c r="G4">
-        <v>0.6278409090909091</v>
+        <v>0.6466876971608833</v>
       </c>
       <c r="H4">
-        <v>0.6278409090909091</v>
+        <v>0.6466876971608833</v>
       </c>
       <c r="I4">
-        <v>0.4943181818181817</v>
+        <v>0.5236593059936909</v>
       </c>
       <c r="J4">
-        <v>0.4426136363636363</v>
+        <v>0.4532579793570768</v>
       </c>
       <c r="K4">
-        <v>31.1</v>
+        <v>28.7</v>
       </c>
       <c r="L4">
-        <v>0.4417613636363636</v>
+        <v>0.4526813880126183</v>
       </c>
       <c r="M4">
-        <v>32.4</v>
+        <v>22.3</v>
       </c>
       <c r="N4">
-        <v>0.06738768718801996</v>
+        <v>0.05480462029982797</v>
       </c>
       <c r="O4">
-        <v>1.041800643086817</v>
+        <v>0.7770034843205575</v>
       </c>
       <c r="P4">
-        <v>32.4</v>
+        <v>22.3</v>
       </c>
       <c r="Q4">
-        <v>0.06738768718801996</v>
+        <v>0.05480462029982797</v>
       </c>
       <c r="R4">
-        <v>1.041800643086817</v>
+        <v>0.7770034843205575</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -898,195 +877,73 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>36.4</v>
+        <v>16.3</v>
       </c>
       <c r="V4">
-        <v>0.07570715474209651</v>
+        <v>0.04005898255099533</v>
       </c>
       <c r="W4">
-        <v>0.1765039727582293</v>
+        <v>0.1556399132321041</v>
       </c>
       <c r="X4">
-        <v>0.0239099698021072</v>
+        <v>0.04958041741100065</v>
       </c>
       <c r="Y4">
-        <v>0.1525940029561221</v>
+        <v>0.1060594958211035</v>
       </c>
       <c r="Z4">
-        <v>0.4305020485537822</v>
+        <v>0.426358935044149</v>
       </c>
       <c r="AA4">
-        <v>0.1905460771723843</v>
+        <v>0.1932505893789462</v>
       </c>
       <c r="AB4">
-        <v>0.02390465953936777</v>
+        <v>0.04946142685365416</v>
       </c>
       <c r="AC4">
-        <v>0.1666414176330165</v>
+        <v>0.143789162525292</v>
       </c>
       <c r="AD4">
-        <v>0.701</v>
+        <v>5.12</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>0.701</v>
+        <v>5.12</v>
       </c>
       <c r="AG4">
-        <v>-35.699</v>
+        <v>-11.18</v>
       </c>
       <c r="AH4">
-        <v>0.001455864058433939</v>
+        <v>0.01242658123392068</v>
       </c>
       <c r="AI4">
-        <v>0.003787121625490948</v>
+        <v>0.02962620067121861</v>
       </c>
       <c r="AJ4">
-        <v>-0.08020426824473546</v>
+        <v>-0.02825229960578187</v>
       </c>
       <c r="AK4">
-        <v>-0.2400723599706794</v>
+        <v>-0.07142857142857144</v>
       </c>
       <c r="AL4">
-        <v>0.025</v>
+        <v>0.044</v>
       </c>
       <c r="AM4">
-        <v>0.025</v>
+        <v>0.044</v>
       </c>
       <c r="AN4">
-        <v>0.01969101123595506</v>
+        <v>0.1510324483775811</v>
       </c>
       <c r="AO4">
-        <v>1392</v>
+        <v>754.5454545454546</v>
       </c>
       <c r="AP4">
-        <v>-1.002780898876404</v>
+        <v>-0.3297935103244838</v>
       </c>
       <c r="AQ4">
-        <v>1392</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Rothschild &amp; Co SCA (ENXTPA:ROTH)</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
-        </is>
-      </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5">
-        <v>0</v>
-      </c>
-      <c r="I5">
-        <v>0.0001504485860155525</v>
-      </c>
-      <c r="J5">
-        <v>0.000131942818029608</v>
-      </c>
-      <c r="K5">
-        <v>529.5</v>
-      </c>
-      <c r="L5">
-        <v>0.1855811019206505</v>
-      </c>
-      <c r="M5">
-        <v>101.6</v>
-      </c>
-      <c r="N5">
-        <v>0.02987444499985298</v>
-      </c>
-      <c r="O5">
-        <v>0.1918791312559018</v>
-      </c>
-      <c r="P5">
-        <v>63.6</v>
-      </c>
-      <c r="Q5">
-        <v>0.01870093210620718</v>
-      </c>
-      <c r="R5">
-        <v>0.1201133144475921</v>
-      </c>
-      <c r="S5">
-        <v>37.99999999999999</v>
-      </c>
-      <c r="T5">
-        <v>0.374015748031496</v>
-      </c>
-      <c r="U5">
-        <v>5755.3</v>
-      </c>
-      <c r="V5">
-        <v>1.692287335705255</v>
-      </c>
-      <c r="W5">
-        <v>0.214164374696651</v>
-      </c>
-      <c r="X5">
-        <v>0.02566312641861677</v>
-      </c>
-      <c r="Y5">
-        <v>0.1885012482780343</v>
-      </c>
-      <c r="Z5">
-        <v>-2.304533636916665</v>
-      </c>
-      <c r="AA5">
-        <v>-0.0003040666622988063</v>
-      </c>
-      <c r="AB5">
-        <v>0.02450662698373873</v>
-      </c>
-      <c r="AC5">
-        <v>-0.02481069364603753</v>
-      </c>
-      <c r="AD5">
-        <v>926.2</v>
-      </c>
-      <c r="AE5">
-        <v>0.5187004719021281</v>
-      </c>
-      <c r="AF5">
-        <v>926.7187004719021</v>
-      </c>
-      <c r="AG5">
-        <v>-4828.581299528098</v>
-      </c>
-      <c r="AH5">
-        <v>0.2141405619609807</v>
-      </c>
-      <c r="AI5">
-        <v>0.2039515133769877</v>
-      </c>
-      <c r="AJ5">
-        <v>3.382114272368858</v>
-      </c>
-      <c r="AK5">
-        <v>3.985683725707488</v>
-      </c>
-      <c r="AL5">
-        <v>0</v>
-      </c>
-      <c r="AM5">
-        <v>0</v>
-      </c>
-      <c r="AN5">
-        <v>1737.711069418386</v>
-      </c>
-      <c r="AP5">
-        <v>-9059.251969095867</v>
+        <v>754.5454545454546</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/france/france_financial_svcs_non_bank_insurance.xlsx
+++ b/research/traditional_assets/database/data/france/france_financial_svcs_non_bank_insurance.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ4"/>
+  <dimension ref="A1:AQ9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,115 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0574</v>
+        <v>0.08825</v>
       </c>
       <c r="E2">
-        <v>0.0271</v>
+        <v>0.0837</v>
+      </c>
+      <c r="F2">
+        <v>0.14755</v>
       </c>
       <c r="G2">
-        <v>0.01257321598331749</v>
+        <v>0.267866826955186</v>
       </c>
       <c r="H2">
-        <v>0.01257321598331749</v>
+        <v>0.2324297068055834</v>
       </c>
       <c r="I2">
-        <v>0.01039663306890468</v>
+        <v>0.2226282745678137</v>
       </c>
       <c r="J2">
-        <v>0.008724913898763158</v>
+        <v>0.1970880234970422</v>
       </c>
       <c r="K2">
-        <v>727.5</v>
+        <v>935.5980000000001</v>
       </c>
       <c r="L2">
-        <v>0.2230979177527676</v>
+        <v>0.1249713484271689</v>
       </c>
       <c r="M2">
-        <v>254.1</v>
+        <v>319.330064</v>
       </c>
       <c r="N2">
-        <v>0.07555304471931494</v>
+        <v>0.01582225800269265</v>
       </c>
       <c r="O2">
-        <v>0.349278350515464</v>
+        <v>0.3413111870696602</v>
       </c>
       <c r="P2">
-        <v>254.1</v>
+        <v>298.630064</v>
       </c>
       <c r="Q2">
-        <v>0.07555304471931494</v>
+        <v>0.01479660843950045</v>
       </c>
       <c r="R2">
-        <v>0.349278350515464</v>
+        <v>0.3191863000989741</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>20.69999999999999</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>0.06482321063261989</v>
       </c>
       <c r="U2">
-        <v>5346.8</v>
+        <v>3009.92</v>
       </c>
       <c r="V2">
-        <v>1.589795432921028</v>
+        <v>0.1491363832484769</v>
       </c>
       <c r="W2">
-        <v>0.1886491135024315</v>
+        <v>-0.1927797833935018</v>
       </c>
       <c r="X2">
-        <v>0.05103199746182066</v>
+        <v>0.0532451124453517</v>
       </c>
       <c r="Y2">
-        <v>0.1376171160406109</v>
+        <v>-0.2460248958388535</v>
       </c>
       <c r="Z2">
-        <v>21.92924055655309</v>
+        <v>2.328150875839916</v>
+      </c>
+      <c r="AA2">
+        <v>0.1523988711194732</v>
       </c>
       <c r="AB2">
-        <v>0.04927074513820548</v>
+        <v>0.05159351298400019</v>
+      </c>
+      <c r="AC2">
+        <v>0.09994881342954146</v>
       </c>
       <c r="AD2">
-        <v>1113.02</v>
+        <v>8946.826000000001</v>
       </c>
       <c r="AE2">
-        <v>0.8230961280435625</v>
+        <v>9.0421122403135</v>
       </c>
       <c r="AF2">
-        <v>1113.843096128043</v>
+        <v>8955.868112240314</v>
       </c>
       <c r="AG2">
-        <v>-4232.956903871956</v>
+        <v>5945.948112240314</v>
       </c>
       <c r="AH2">
-        <v>0.2487898982011916</v>
+        <v>0.3073583158102532</v>
       </c>
       <c r="AI2">
-        <v>0.2197083847931514</v>
+        <v>0.4465446855473354</v>
       </c>
       <c r="AJ2">
-        <v>4.866827598640279</v>
+        <v>0.2275675278548019</v>
       </c>
       <c r="AK2">
-        <v>15.27278175191167</v>
+        <v>0.3488176277453885</v>
       </c>
       <c r="AL2">
-        <v>0.044</v>
+        <v>128.752</v>
       </c>
       <c r="AM2">
-        <v>0.044</v>
+        <v>-85.75099999999998</v>
       </c>
       <c r="AN2">
-        <v>32.01369114390083</v>
+        <v>4.9603315453172</v>
       </c>
       <c r="AO2">
-        <v>754.5454545454546</v>
+        <v>12.92341089847148</v>
       </c>
       <c r="AP2">
-        <v>-121.7521472624028</v>
+        <v>3.296574001547016</v>
       </c>
       <c r="AQ2">
-        <v>754.5454545454546</v>
+        <v>-19.40403027369944</v>
       </c>
     </row>
     <row r="3">
@@ -707,7 +716,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Rothschild &amp; Co SCA (ENXTPA:ROTH)</t>
+          <t>Imprimerie Chirat Société Anonyme (ENXTPA:MLIMP)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -715,41 +724,47 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="D3">
+        <v>0.0133</v>
+      </c>
+      <c r="E3">
+        <v>-0.154</v>
+      </c>
       <c r="G3">
-        <v>0</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="I3">
-        <v>0.0002196656057517709</v>
+        <v>0.02635555555555556</v>
       </c>
       <c r="J3">
-        <v>0.0001785557411154709</v>
+        <v>0.02047094220110847</v>
       </c>
       <c r="K3">
-        <v>698.8</v>
+        <v>0.654</v>
       </c>
       <c r="L3">
-        <v>0.2185457388584832</v>
+        <v>0.02906666666666667</v>
       </c>
       <c r="M3">
-        <v>231.8</v>
+        <v>0.330064</v>
       </c>
       <c r="N3">
-        <v>0.07840882183810845</v>
+        <v>0.05537986577181209</v>
       </c>
       <c r="O3">
-        <v>0.3317115054378936</v>
+        <v>0.5046850152905199</v>
       </c>
       <c r="P3">
-        <v>231.8</v>
+        <v>0.330064</v>
       </c>
       <c r="Q3">
-        <v>0.07840882183810845</v>
+        <v>0.05537986577181209</v>
       </c>
       <c r="R3">
-        <v>0.3317115054378936</v>
+        <v>0.5046850152905199</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -758,58 +773,52 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>5330.5</v>
+        <v>0</v>
       </c>
       <c r="V3">
-        <v>1.803098467679193</v>
-      </c>
-      <c r="W3">
-        <v>0.221658313772759</v>
+        <v>0</v>
       </c>
       <c r="X3">
-        <v>0.05248357751264067</v>
-      </c>
-      <c r="Y3">
-        <v>0.1691747362601183</v>
+        <v>0.0515462371428773</v>
       </c>
       <c r="AB3">
-        <v>0.0490800634227568</v>
+        <v>0.0515462371428773</v>
       </c>
       <c r="AD3">
-        <v>1107.9</v>
+        <v>0</v>
       </c>
       <c r="AE3">
-        <v>0.8230961280435625</v>
+        <v>0</v>
       </c>
       <c r="AF3">
-        <v>1108.723096128044</v>
+        <v>0</v>
       </c>
       <c r="AG3">
-        <v>-4221.776903871956</v>
+        <v>0</v>
       </c>
       <c r="AH3">
-        <v>0.2727470594654451</v>
-      </c>
-      <c r="AI3">
-        <v>0.2264168164467121</v>
+        <v>0</v>
       </c>
       <c r="AJ3">
-        <v>3.336115334033094</v>
-      </c>
-      <c r="AK3">
-        <v>9.73484376543705</v>
+        <v>0</v>
       </c>
       <c r="AL3">
-        <v>0</v>
+        <v>0.044</v>
       </c>
       <c r="AM3">
-        <v>0</v>
+        <v>0.04099999999999999</v>
       </c>
       <c r="AN3">
-        <v>1277.854671280277</v>
+        <v>0</v>
+      </c>
+      <c r="AO3">
+        <v>13.47727272727273</v>
       </c>
       <c r="AP3">
-        <v>-4869.40819362394</v>
+        <v>0</v>
+      </c>
+      <c r="AQ3">
+        <v>14.46341463414634</v>
       </c>
     </row>
     <row r="4">
@@ -820,130 +829,740 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>Edenred SE (ENXTPA:EDEN)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D4">
+        <v>0.108</v>
+      </c>
+      <c r="E4">
+        <v>0.116</v>
+      </c>
+      <c r="F4">
+        <v>0.207</v>
+      </c>
+      <c r="G4">
+        <v>0.3303000386315835</v>
+      </c>
+      <c r="H4">
+        <v>0.3303000386315835</v>
+      </c>
+      <c r="I4">
+        <v>0.3083229600377731</v>
+      </c>
+      <c r="J4">
+        <v>0.2115038680069226</v>
+      </c>
+      <c r="K4">
+        <v>456.3</v>
+      </c>
+      <c r="L4">
+        <v>0.1958621281710092</v>
+      </c>
+      <c r="M4">
+        <v>292.5</v>
+      </c>
+      <c r="N4">
+        <v>0.01960942056676254</v>
+      </c>
+      <c r="O4">
+        <v>0.641025641025641</v>
+      </c>
+      <c r="P4">
+        <v>271.8</v>
+      </c>
+      <c r="Q4">
+        <v>0.01822167695742242</v>
+      </c>
+      <c r="R4">
+        <v>0.5956607495069034</v>
+      </c>
+      <c r="S4">
+        <v>20.69999999999999</v>
+      </c>
+      <c r="T4">
+        <v>0.07076923076923074</v>
+      </c>
+      <c r="U4">
+        <v>1494.5</v>
+      </c>
+      <c r="V4">
+        <v>0.1001924069641935</v>
+      </c>
+      <c r="W4">
+        <v>-0.4796594134342479</v>
+      </c>
+      <c r="X4">
+        <v>0.05475554795303157</v>
+      </c>
+      <c r="Y4">
+        <v>-0.5344149613872795</v>
+      </c>
+      <c r="Z4">
+        <v>79.78424657534171</v>
+      </c>
+      <c r="AA4">
+        <v>16.87467675670284</v>
+      </c>
+      <c r="AB4">
+        <v>0.05159351298400019</v>
+      </c>
+      <c r="AC4">
+        <v>16.82308324371884</v>
+      </c>
+      <c r="AD4">
+        <v>5007.6</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>5007.6</v>
+      </c>
+      <c r="AG4">
+        <v>3513.1</v>
+      </c>
+      <c r="AH4">
+        <v>0.251336334753738</v>
+      </c>
+      <c r="AI4">
+        <v>1.135690472410587</v>
+      </c>
+      <c r="AJ4">
+        <v>0.1906247626075727</v>
+      </c>
+      <c r="AK4">
+        <v>1.205262796761356</v>
+      </c>
+      <c r="AL4">
+        <v>81.90000000000001</v>
+      </c>
+      <c r="AM4">
+        <v>-110.2</v>
+      </c>
+      <c r="AN4">
+        <v>5.828212290502793</v>
+      </c>
+      <c r="AO4">
+        <v>8.770451770451769</v>
+      </c>
+      <c r="AP4">
+        <v>4.088803538175047</v>
+      </c>
+      <c r="AQ4">
+        <v>-6.518148820326679</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Worldline SA (ENXTPA:WLN)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D5">
+        <v>0.233</v>
+      </c>
+      <c r="E5">
+        <v>0.304</v>
+      </c>
+      <c r="F5">
+        <v>0.08810000000000001</v>
+      </c>
+      <c r="G5">
+        <v>0.2408428200519273</v>
+      </c>
+      <c r="H5">
+        <v>0.1878570001997204</v>
+      </c>
+      <c r="I5">
+        <v>0.1845000154887033</v>
+      </c>
+      <c r="J5">
+        <v>0.1354683603887684</v>
+      </c>
+      <c r="K5">
+        <v>461.1</v>
+      </c>
+      <c r="L5">
+        <v>0.0920910724985021</v>
+      </c>
+      <c r="M5">
+        <v>-0</v>
+      </c>
+      <c r="N5">
+        <v>-0</v>
+      </c>
+      <c r="O5">
+        <v>-0</v>
+      </c>
+      <c r="P5">
+        <v>-0</v>
+      </c>
+      <c r="Q5">
+        <v>-0</v>
+      </c>
+      <c r="R5">
+        <v>-0</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>1493.7</v>
+      </c>
+      <c r="V5">
+        <v>0.3047558810927713</v>
+      </c>
+      <c r="W5">
+        <v>0.04766975436274916</v>
+      </c>
+      <c r="X5">
+        <v>0.05917857509450157</v>
+      </c>
+      <c r="Y5">
+        <v>-0.01150882073175241</v>
+      </c>
+      <c r="Z5">
+        <v>1.658418124705175</v>
+      </c>
+      <c r="AA5">
+        <v>0.2246631841928262</v>
+      </c>
+      <c r="AB5">
+        <v>0.05296724287651144</v>
+      </c>
+      <c r="AC5">
+        <v>0.1716959413163148</v>
+      </c>
+      <c r="AD5">
+        <v>3904.1</v>
+      </c>
+      <c r="AE5">
+        <v>9.0421122403135</v>
+      </c>
+      <c r="AF5">
+        <v>3913.142112240314</v>
+      </c>
+      <c r="AG5">
+        <v>2419.442112240314</v>
+      </c>
+      <c r="AH5">
+        <v>0.443946657362043</v>
+      </c>
+      <c r="AI5">
+        <v>0.2539197203999785</v>
+      </c>
+      <c r="AJ5">
+        <v>0.3304913730255565</v>
+      </c>
+      <c r="AK5">
+        <v>0.173844939444748</v>
+      </c>
+      <c r="AL5">
+        <v>44.9</v>
+      </c>
+      <c r="AM5">
+        <v>22.5</v>
+      </c>
+      <c r="AN5">
+        <v>4.253295565965791</v>
+      </c>
+      <c r="AO5">
+        <v>20.51224944320713</v>
+      </c>
+      <c r="AP5">
+        <v>2.635844985554324</v>
+      </c>
+      <c r="AQ5">
+        <v>40.93333333333333</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
           <t>ABC arbitrage SA (ENXTPA:ABCA)</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D4">
-        <v>0.0574</v>
-      </c>
-      <c r="E4">
-        <v>0.0271</v>
-      </c>
-      <c r="G4">
-        <v>0.6466876971608833</v>
-      </c>
-      <c r="H4">
-        <v>0.6466876971608833</v>
-      </c>
-      <c r="I4">
-        <v>0.5236593059936909</v>
-      </c>
-      <c r="J4">
-        <v>0.4532579793570768</v>
-      </c>
-      <c r="K4">
-        <v>28.7</v>
-      </c>
-      <c r="L4">
-        <v>0.4526813880126183</v>
-      </c>
-      <c r="M4">
-        <v>22.3</v>
-      </c>
-      <c r="N4">
-        <v>0.05480462029982797</v>
-      </c>
-      <c r="O4">
-        <v>0.7770034843205575</v>
-      </c>
-      <c r="P4">
-        <v>22.3</v>
-      </c>
-      <c r="Q4">
-        <v>0.05480462029982797</v>
-      </c>
-      <c r="R4">
-        <v>0.7770034843205575</v>
-      </c>
-      <c r="S4">
-        <v>0</v>
-      </c>
-      <c r="T4">
-        <v>0</v>
-      </c>
-      <c r="U4">
-        <v>16.3</v>
-      </c>
-      <c r="V4">
-        <v>0.04005898255099533</v>
-      </c>
-      <c r="W4">
-        <v>0.1556399132321041</v>
-      </c>
-      <c r="X4">
-        <v>0.04958041741100065</v>
-      </c>
-      <c r="Y4">
-        <v>0.1060594958211035</v>
-      </c>
-      <c r="Z4">
-        <v>0.426358935044149</v>
-      </c>
-      <c r="AA4">
-        <v>0.1932505893789462</v>
-      </c>
-      <c r="AB4">
-        <v>0.04946142685365416</v>
-      </c>
-      <c r="AC4">
-        <v>0.143789162525292</v>
-      </c>
-      <c r="AD4">
-        <v>5.12</v>
-      </c>
-      <c r="AE4">
-        <v>0</v>
-      </c>
-      <c r="AF4">
-        <v>5.12</v>
-      </c>
-      <c r="AG4">
-        <v>-11.18</v>
-      </c>
-      <c r="AH4">
-        <v>0.01242658123392068</v>
-      </c>
-      <c r="AI4">
-        <v>0.02962620067121861</v>
-      </c>
-      <c r="AJ4">
-        <v>-0.02825229960578187</v>
-      </c>
-      <c r="AK4">
-        <v>-0.07142857142857144</v>
-      </c>
-      <c r="AL4">
-        <v>0.044</v>
-      </c>
-      <c r="AM4">
-        <v>0.044</v>
-      </c>
-      <c r="AN4">
-        <v>0.1510324483775811</v>
-      </c>
-      <c r="AO4">
-        <v>754.5454545454546</v>
-      </c>
-      <c r="AP4">
-        <v>-0.3297935103244838</v>
-      </c>
-      <c r="AQ4">
-        <v>754.5454545454546</v>
+      <c r="D6">
+        <v>0.06849999999999999</v>
+      </c>
+      <c r="E6">
+        <v>0.05139999999999999</v>
+      </c>
+      <c r="G6">
+        <v>0.581056466302368</v>
+      </c>
+      <c r="H6">
+        <v>0.581056466302368</v>
+      </c>
+      <c r="I6">
+        <v>0.4316939890710382</v>
+      </c>
+      <c r="J6">
+        <v>0.4316939890710382</v>
+      </c>
+      <c r="K6">
+        <v>23.7</v>
+      </c>
+      <c r="L6">
+        <v>0.4316939890710382</v>
+      </c>
+      <c r="M6">
+        <v>26.5</v>
+      </c>
+      <c r="N6">
+        <v>0.08386075949367089</v>
+      </c>
+      <c r="O6">
+        <v>1.118143459915612</v>
+      </c>
+      <c r="P6">
+        <v>26.5</v>
+      </c>
+      <c r="Q6">
+        <v>0.08386075949367089</v>
+      </c>
+      <c r="R6">
+        <v>1.118143459915612</v>
+      </c>
+      <c r="S6">
+        <v>0</v>
+      </c>
+      <c r="T6">
+        <v>0</v>
+      </c>
+      <c r="U6">
+        <v>18.4</v>
+      </c>
+      <c r="V6">
+        <v>0.05822784810126582</v>
+      </c>
+      <c r="W6">
+        <v>0.1413237924865832</v>
+      </c>
+      <c r="X6">
+        <v>0.05172532984197342</v>
+      </c>
+      <c r="Y6">
+        <v>0.08959846264460977</v>
+      </c>
+      <c r="Z6">
+        <v>0.3507538972655252</v>
+      </c>
+      <c r="AA6">
+        <v>0.1514183490927677</v>
+      </c>
+      <c r="AB6">
+        <v>0.05146953566322627</v>
+      </c>
+      <c r="AC6">
+        <v>0.09994881342954146</v>
+      </c>
+      <c r="AD6">
+        <v>5.92</v>
+      </c>
+      <c r="AE6">
+        <v>0</v>
+      </c>
+      <c r="AF6">
+        <v>5.92</v>
+      </c>
+      <c r="AG6">
+        <v>-12.48</v>
+      </c>
+      <c r="AH6">
+        <v>0.018389662027833</v>
+      </c>
+      <c r="AI6">
+        <v>0.03283052351375332</v>
+      </c>
+      <c r="AJ6">
+        <v>-0.04111755403268318</v>
+      </c>
+      <c r="AK6">
+        <v>-0.07707509881422923</v>
+      </c>
+      <c r="AL6">
+        <v>0.074</v>
+      </c>
+      <c r="AM6">
+        <v>0.074</v>
+      </c>
+      <c r="AN6">
+        <v>0.240650406504065</v>
+      </c>
+      <c r="AO6">
+        <v>320.2702702702703</v>
+      </c>
+      <c r="AP6">
+        <v>-0.5073170731707316</v>
+      </c>
+      <c r="AQ6">
+        <v>320.2702702702703</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>HiPay Group SA (ENXTPA:ALHYP)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D7">
+        <v>0.198</v>
+      </c>
+      <c r="G7">
+        <v>-0.04728571428571429</v>
+      </c>
+      <c r="H7">
+        <v>-0.04728571428571429</v>
+      </c>
+      <c r="I7">
+        <v>0.02314285714285715</v>
+      </c>
+      <c r="J7">
+        <v>0.02314285714285715</v>
+      </c>
+      <c r="K7">
+        <v>-5.34</v>
+      </c>
+      <c r="L7">
+        <v>-0.07628571428571429</v>
+      </c>
+      <c r="M7">
+        <v>-0</v>
+      </c>
+      <c r="N7">
+        <v>-0</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <v>-0</v>
+      </c>
+      <c r="Q7">
+        <v>-0</v>
+      </c>
+      <c r="R7">
+        <v>0</v>
+      </c>
+      <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="U7">
+        <v>2.21</v>
+      </c>
+      <c r="V7">
+        <v>0.05695876288659794</v>
+      </c>
+      <c r="W7">
+        <v>-0.1927797833935018</v>
+      </c>
+      <c r="X7">
+        <v>0.0585928038107824</v>
+      </c>
+      <c r="Y7">
+        <v>-0.2513725872042842</v>
+      </c>
+      <c r="Z7">
+        <v>6.585136406396988</v>
+      </c>
+      <c r="AA7">
+        <v>0.1523988711194732</v>
+      </c>
+      <c r="AB7">
+        <v>0.05247546044312006</v>
+      </c>
+      <c r="AC7">
+        <v>0.09992341067635312</v>
+      </c>
+      <c r="AD7">
+        <v>28.6</v>
+      </c>
+      <c r="AE7">
+        <v>0</v>
+      </c>
+      <c r="AF7">
+        <v>28.6</v>
+      </c>
+      <c r="AG7">
+        <v>26.39</v>
+      </c>
+      <c r="AH7">
+        <v>0.4243323442136498</v>
+      </c>
+      <c r="AI7">
+        <v>0.5510597302504817</v>
+      </c>
+      <c r="AJ7">
+        <v>0.4048166896763307</v>
+      </c>
+      <c r="AK7">
+        <v>0.531092775206279</v>
+      </c>
+      <c r="AL7">
+        <v>1.81</v>
+      </c>
+      <c r="AM7">
+        <v>1.81</v>
+      </c>
+      <c r="AN7">
+        <v>42.6865671641791</v>
+      </c>
+      <c r="AO7">
+        <v>0.8950276243093923</v>
+      </c>
+      <c r="AP7">
+        <v>39.38805970149254</v>
+      </c>
+      <c r="AQ7">
+        <v>0.8950276243093923</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>BD Multimedia SA (ENXTPA:ALBDM)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D8">
+        <v>-0.172</v>
+      </c>
+      <c r="G8">
+        <v>-0.4375000000000001</v>
+      </c>
+      <c r="H8">
+        <v>-0.4375000000000001</v>
+      </c>
+      <c r="I8">
+        <v>-0.5125000000000001</v>
+      </c>
+      <c r="J8">
+        <v>-0.5125000000000001</v>
+      </c>
+      <c r="K8">
+        <v>-0.76</v>
+      </c>
+      <c r="L8">
+        <v>-0.3166666666666667</v>
+      </c>
+      <c r="M8">
+        <v>-0</v>
+      </c>
+      <c r="N8">
+        <v>-0</v>
+      </c>
+      <c r="O8">
+        <v>0</v>
+      </c>
+      <c r="P8">
+        <v>-0</v>
+      </c>
+      <c r="Q8">
+        <v>-0</v>
+      </c>
+      <c r="R8">
+        <v>0</v>
+      </c>
+      <c r="S8">
+        <v>0</v>
+      </c>
+      <c r="U8">
+        <v>1.11</v>
+      </c>
+      <c r="V8">
+        <v>0.3255131964809384</v>
+      </c>
+      <c r="W8">
+        <v>-0.3220338983050848</v>
+      </c>
+      <c r="X8">
+        <v>0.0532451124453517</v>
+      </c>
+      <c r="Y8">
+        <v>-0.3752790107504365</v>
+      </c>
+      <c r="Z8">
+        <v>16.00000000000002</v>
+      </c>
+      <c r="AA8">
+        <v>-8.20000000000001</v>
+      </c>
+      <c r="AB8">
+        <v>0.05187667734156189</v>
+      </c>
+      <c r="AC8">
+        <v>-8.251876677341572</v>
+      </c>
+      <c r="AD8">
+        <v>0.606</v>
+      </c>
+      <c r="AE8">
+        <v>0</v>
+      </c>
+      <c r="AF8">
+        <v>0.606</v>
+      </c>
+      <c r="AG8">
+        <v>-0.5040000000000001</v>
+      </c>
+      <c r="AH8">
+        <v>0.1508964143426295</v>
+      </c>
+      <c r="AI8">
+        <v>0.1748413156376226</v>
+      </c>
+      <c r="AJ8">
+        <v>-0.1734342739160358</v>
+      </c>
+      <c r="AK8">
+        <v>-0.2139219015280136</v>
+      </c>
+      <c r="AL8">
+        <v>0.024</v>
+      </c>
+      <c r="AM8">
+        <v>0.024</v>
+      </c>
+      <c r="AN8">
+        <v>-0.531578947368421</v>
+      </c>
+      <c r="AO8">
+        <v>-51.25</v>
+      </c>
+      <c r="AP8">
+        <v>0.4421052631578949</v>
+      </c>
+      <c r="AQ8">
+        <v>-51.25</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>CFI-Compagnie Foncière Internationale (ENXTPA:CFI)</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="K9">
+        <v>-0.056</v>
+      </c>
+      <c r="M9">
+        <v>-0</v>
+      </c>
+      <c r="N9">
+        <v>-0</v>
+      </c>
+      <c r="O9">
+        <v>0</v>
+      </c>
+      <c r="P9">
+        <v>-0</v>
+      </c>
+      <c r="Q9">
+        <v>-0</v>
+      </c>
+      <c r="R9">
+        <v>0</v>
+      </c>
+      <c r="S9">
+        <v>0</v>
+      </c>
+      <c r="U9">
+        <v>0</v>
+      </c>
+      <c r="V9">
+        <v>0</v>
+      </c>
+      <c r="X9">
+        <v>0.0515462371428773</v>
+      </c>
+      <c r="AB9">
+        <v>0.0515462371428773</v>
+      </c>
+      <c r="AD9">
+        <v>0</v>
+      </c>
+      <c r="AE9">
+        <v>0</v>
+      </c>
+      <c r="AF9">
+        <v>0</v>
+      </c>
+      <c r="AG9">
+        <v>0</v>
+      </c>
+      <c r="AH9">
+        <v>0</v>
+      </c>
+      <c r="AJ9">
+        <v>0</v>
+      </c>
+      <c r="AL9">
+        <v>0</v>
+      </c>
+      <c r="AM9">
+        <v>0</v>
+      </c>
+      <c r="AN9">
+        <v>-0</v>
+      </c>
+      <c r="AP9">
+        <v>-0</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/france/france_financial_svcs_non_bank_insurance.xlsx
+++ b/research/traditional_assets/database/data/france/france_financial_svcs_non_bank_insurance.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ9"/>
+  <dimension ref="A1:AQ5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,124 +588,118 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.08825</v>
+        <v>0.148</v>
       </c>
       <c r="E2">
-        <v>0.0837</v>
+        <v>0.0168</v>
       </c>
       <c r="F2">
-        <v>0.14755</v>
+        <v>0.172</v>
       </c>
       <c r="G2">
-        <v>0.267866826955186</v>
+        <v>0.2615230905861456</v>
       </c>
       <c r="H2">
-        <v>0.2324297068055834</v>
+        <v>0.2309502664298402</v>
       </c>
       <c r="I2">
-        <v>0.2226282745678137</v>
+        <v>0.1723173866566689</v>
       </c>
       <c r="J2">
-        <v>0.1970880234970422</v>
+        <v>0.1254406400277555</v>
       </c>
       <c r="K2">
-        <v>935.5980000000001</v>
+        <v>-525.1</v>
       </c>
       <c r="L2">
-        <v>0.1249713484271689</v>
+        <v>-0.05829262877442274</v>
       </c>
       <c r="M2">
-        <v>319.330064</v>
+        <v>589.0633</v>
       </c>
       <c r="N2">
-        <v>0.01582225800269265</v>
+        <v>0.04416693908766458</v>
       </c>
       <c r="O2">
-        <v>0.3413111870696602</v>
+        <v>-1.121811654922872</v>
       </c>
       <c r="P2">
-        <v>298.630064</v>
+        <v>346.8633</v>
       </c>
       <c r="Q2">
-        <v>0.01479660843950045</v>
+        <v>0.02600720541043097</v>
       </c>
       <c r="R2">
-        <v>0.3191863000989741</v>
+        <v>-0.6605661778708817</v>
       </c>
       <c r="S2">
-        <v>20.69999999999999</v>
+        <v>242.2</v>
       </c>
       <c r="T2">
-        <v>0.06482321063261989</v>
+        <v>0.4111612453194758</v>
       </c>
       <c r="U2">
-        <v>3009.92</v>
+        <v>5428.4</v>
       </c>
       <c r="V2">
-        <v>0.1491363832484769</v>
+        <v>0.4070119665297063</v>
       </c>
       <c r="W2">
-        <v>-0.1927797833935018</v>
+        <v>-0.09696875060995842</v>
       </c>
       <c r="X2">
-        <v>0.0532451124453517</v>
+        <v>0.06438550124326707</v>
       </c>
       <c r="Y2">
-        <v>-0.2460248958388535</v>
+        <v>-0.1613542518532255</v>
       </c>
       <c r="Z2">
-        <v>2.328150875839916</v>
-      </c>
-      <c r="AA2">
-        <v>0.1523988711194732</v>
+        <v>5.535975249133169</v>
       </c>
       <c r="AB2">
-        <v>0.05159351298400019</v>
-      </c>
-      <c r="AC2">
-        <v>0.09994881342954146</v>
+        <v>0.05742288563080732</v>
       </c>
       <c r="AD2">
-        <v>8946.826000000001</v>
+        <v>11265.9</v>
       </c>
       <c r="AE2">
-        <v>9.0421122403135</v>
+        <v>8.674904983631425</v>
       </c>
       <c r="AF2">
-        <v>8955.868112240314</v>
+        <v>11274.57490498363</v>
       </c>
       <c r="AG2">
-        <v>5945.948112240314</v>
+        <v>5846.174904983633</v>
       </c>
       <c r="AH2">
-        <v>0.3073583158102532</v>
+        <v>0.4580967828817842</v>
       </c>
       <c r="AI2">
-        <v>0.4465446855473354</v>
+        <v>0.5362926844275527</v>
       </c>
       <c r="AJ2">
-        <v>0.2275675278548019</v>
+        <v>0.304752158258913</v>
       </c>
       <c r="AK2">
-        <v>0.3488176277453885</v>
+        <v>0.3748803647762409</v>
       </c>
       <c r="AL2">
-        <v>128.752</v>
+        <v>290</v>
       </c>
       <c r="AM2">
-        <v>-85.75099999999998</v>
+        <v>-77.40000000000003</v>
       </c>
       <c r="AN2">
-        <v>4.9603315453172</v>
+        <v>5.563215098737327</v>
       </c>
       <c r="AO2">
-        <v>12.92341089847148</v>
+        <v>5.334137931034483</v>
       </c>
       <c r="AP2">
-        <v>3.296574001547016</v>
+        <v>2.886900158998766</v>
       </c>
       <c r="AQ2">
-        <v>-19.40403027369944</v>
+        <v>-19.98578811369508</v>
       </c>
     </row>
     <row r="3">
@@ -716,7 +710,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Imprimerie Chirat Société Anonyme (ENXTPA:MLIMP)</t>
+          <t>Edenred SE (ENXTPA:EDEN)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -725,100 +719,115 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0133</v>
+        <v>0.118</v>
       </c>
       <c r="E3">
-        <v>-0.154</v>
+        <v>0.0168</v>
+      </c>
+      <c r="F3">
+        <v>0.172</v>
       </c>
       <c r="G3">
-        <v>0.1111111111111111</v>
+        <v>0.2668955480091055</v>
       </c>
       <c r="H3">
-        <v>0.1111111111111111</v>
+        <v>0.2668955480091055</v>
       </c>
       <c r="I3">
-        <v>0.02635555555555556</v>
+        <v>0.2319289472702168</v>
       </c>
       <c r="J3">
-        <v>0.02047094220110847</v>
+        <v>0.1344542220413389</v>
       </c>
       <c r="K3">
-        <v>0.654</v>
+        <v>321.4</v>
       </c>
       <c r="L3">
-        <v>0.02906666666666667</v>
+        <v>0.1199387991193044</v>
       </c>
       <c r="M3">
-        <v>0.330064</v>
+        <v>496.1</v>
       </c>
       <c r="N3">
-        <v>0.05537986577181209</v>
+        <v>0.06185168561739477</v>
       </c>
       <c r="O3">
-        <v>0.5046850152905199</v>
+        <v>1.543559427504667</v>
       </c>
       <c r="P3">
-        <v>0.330064</v>
+        <v>290.4</v>
       </c>
       <c r="Q3">
-        <v>0.05537986577181209</v>
+        <v>0.03620586475164572</v>
       </c>
       <c r="R3">
-        <v>0.5046850152905199</v>
+        <v>0.9035469819539514</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>205.7</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>0.4146341463414634</v>
       </c>
       <c r="U3">
-        <v>0</v>
+        <v>1591.1</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>0.1983717334929184</v>
+      </c>
+      <c r="W3">
+        <v>-0.4440453163857419</v>
       </c>
       <c r="X3">
-        <v>0.0515462371428773</v>
+        <v>0.06438550124326707</v>
+      </c>
+      <c r="Y3">
+        <v>-0.508430817629009</v>
       </c>
       <c r="AB3">
-        <v>0.0515462371428773</v>
+        <v>0.05689814306340023</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>5474.1</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>5474.1</v>
       </c>
       <c r="AG3">
-        <v>0</v>
+        <v>3883</v>
       </c>
       <c r="AH3">
-        <v>0</v>
+        <v>0.4056421314718894</v>
+      </c>
+      <c r="AI3">
+        <v>1.192588396766955</v>
       </c>
       <c r="AJ3">
-        <v>0</v>
+        <v>0.3261983568272316</v>
+      </c>
+      <c r="AK3">
+        <v>1.294764921640547</v>
       </c>
       <c r="AL3">
-        <v>0.044</v>
+        <v>174.6</v>
       </c>
       <c r="AM3">
-        <v>0.04099999999999999</v>
+        <v>-111.5</v>
       </c>
       <c r="AN3">
-        <v>0</v>
+        <v>7.236087243886319</v>
       </c>
       <c r="AO3">
-        <v>13.47727272727273</v>
+        <v>3.559564719358534</v>
       </c>
       <c r="AP3">
-        <v>0</v>
+        <v>5.132848645076009</v>
       </c>
       <c r="AQ3">
-        <v>14.46341463414634</v>
+        <v>-5.573991031390134</v>
       </c>
     </row>
     <row r="4">
@@ -829,7 +838,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Edenred SE (ENXTPA:EDEN)</t>
+          <t>Pluxee N.V. (ENXTPA:PLX)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -837,125 +846,110 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D4">
-        <v>0.108</v>
-      </c>
-      <c r="E4">
-        <v>0.116</v>
-      </c>
       <c r="F4">
-        <v>0.207</v>
+        <v>0.195</v>
       </c>
       <c r="G4">
-        <v>0.3303000386315835</v>
+        <v>0.3281028170066503</v>
       </c>
       <c r="H4">
-        <v>0.3303000386315835</v>
+        <v>0.3281028170066503</v>
       </c>
       <c r="I4">
-        <v>0.3083229600377731</v>
+        <v>0.2810281700665023</v>
       </c>
       <c r="J4">
-        <v>0.2115038680069226</v>
+        <v>0.1697878527485119</v>
       </c>
       <c r="K4">
-        <v>456.3</v>
+        <v>147.1</v>
       </c>
       <c r="L4">
-        <v>0.1958621281710092</v>
+        <v>0.109915564522155</v>
       </c>
       <c r="M4">
-        <v>292.5</v>
+        <v>92.9633</v>
       </c>
       <c r="N4">
-        <v>0.01960942056676254</v>
+        <v>0.03287942986489354</v>
       </c>
       <c r="O4">
-        <v>0.641025641025641</v>
+        <v>0.6319734874235214</v>
       </c>
       <c r="P4">
-        <v>271.8</v>
+        <v>56.4633</v>
       </c>
       <c r="Q4">
-        <v>0.01822167695742242</v>
+        <v>0.019970043149183</v>
       </c>
       <c r="R4">
-        <v>0.5956607495069034</v>
+        <v>0.3838429639700884</v>
       </c>
       <c r="S4">
-        <v>20.69999999999999</v>
+        <v>36.5</v>
       </c>
       <c r="T4">
-        <v>0.07076923076923074</v>
+        <v>0.3926280585994688</v>
       </c>
       <c r="U4">
-        <v>1494.5</v>
+        <v>1571.7</v>
       </c>
       <c r="V4">
-        <v>0.1001924069641935</v>
+        <v>0.5558817287967744</v>
       </c>
       <c r="W4">
-        <v>-0.4796594134342479</v>
+        <v>3.225877192982456</v>
       </c>
       <c r="X4">
-        <v>0.05475554795303157</v>
+        <v>0.06235277660478426</v>
       </c>
       <c r="Y4">
-        <v>-0.5344149613872795</v>
-      </c>
-      <c r="Z4">
-        <v>79.78424657534171</v>
-      </c>
-      <c r="AA4">
-        <v>16.87467675670284</v>
+        <v>3.163524416377672</v>
       </c>
       <c r="AB4">
-        <v>0.05159351298400019</v>
-      </c>
-      <c r="AC4">
-        <v>16.82308324371884</v>
+        <v>0.05742288563080732</v>
       </c>
       <c r="AD4">
-        <v>5007.6</v>
+        <v>1306.3</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>5007.6</v>
+        <v>1306.3</v>
       </c>
       <c r="AG4">
-        <v>3513.1</v>
+        <v>-265.4000000000001</v>
       </c>
       <c r="AH4">
-        <v>0.251336334753738</v>
+        <v>0.3160122892324068</v>
       </c>
       <c r="AI4">
-        <v>1.135690472410587</v>
+        <v>0.7694074684886324</v>
       </c>
       <c r="AJ4">
-        <v>0.1906247626075727</v>
+        <v>-0.1035909445745512</v>
       </c>
       <c r="AK4">
-        <v>1.205262796761356</v>
+        <v>-2.104678826328313</v>
       </c>
       <c r="AL4">
-        <v>81.90000000000001</v>
+        <v>57.5</v>
       </c>
       <c r="AM4">
-        <v>-110.2</v>
+        <v>8.799999999999997</v>
       </c>
       <c r="AN4">
-        <v>5.828212290502793</v>
+        <v>2.974948758824869</v>
       </c>
       <c r="AO4">
-        <v>8.770451770451769</v>
+        <v>6.540869565217392</v>
       </c>
       <c r="AP4">
-        <v>4.088803538175047</v>
+        <v>-0.6044181279890687</v>
       </c>
       <c r="AQ4">
-        <v>-6.518148820326679</v>
+        <v>42.73863636363638</v>
       </c>
     </row>
     <row r="5">
@@ -975,31 +969,28 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.233</v>
-      </c>
-      <c r="E5">
-        <v>0.304</v>
+        <v>0.178</v>
       </c>
       <c r="F5">
-        <v>0.08810000000000001</v>
+        <v>0.047</v>
       </c>
       <c r="G5">
-        <v>0.2408428200519273</v>
+        <v>0.2407815631262525</v>
       </c>
       <c r="H5">
-        <v>0.1878570001997204</v>
+        <v>0.1855911823647295</v>
       </c>
       <c r="I5">
-        <v>0.1845000154887033</v>
+        <v>0.1111493024054657</v>
       </c>
       <c r="J5">
-        <v>0.1354683603887684</v>
+        <v>0.1111493024054657</v>
       </c>
       <c r="K5">
-        <v>461.1</v>
+        <v>-993.6</v>
       </c>
       <c r="L5">
-        <v>0.0920910724985021</v>
+        <v>-0.1991182364729459</v>
       </c>
       <c r="M5">
         <v>-0</v>
@@ -1008,7 +999,7 @@
         <v>-0</v>
       </c>
       <c r="O5">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P5">
         <v>-0</v>
@@ -1017,552 +1008,79 @@
         <v>-0</v>
       </c>
       <c r="R5">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S5">
         <v>0</v>
       </c>
       <c r="U5">
-        <v>1493.7</v>
+        <v>2265.6</v>
       </c>
       <c r="V5">
-        <v>0.3047558810927713</v>
+        <v>0.9102450783447167</v>
       </c>
       <c r="W5">
-        <v>0.04766975436274916</v>
+        <v>-0.09696875060995842</v>
       </c>
       <c r="X5">
-        <v>0.05917857509450157</v>
+        <v>0.07474052170629047</v>
       </c>
       <c r="Y5">
-        <v>-0.01150882073175241</v>
+        <v>-0.1717092723162489</v>
       </c>
       <c r="Z5">
-        <v>1.658418124705175</v>
+        <v>3.066664797199657</v>
       </c>
       <c r="AA5">
-        <v>0.2246631841928262</v>
+        <v>0.3408576529201408</v>
       </c>
       <c r="AB5">
-        <v>0.05296724287651144</v>
+        <v>0.05836930247064742</v>
       </c>
       <c r="AC5">
-        <v>0.1716959413163148</v>
+        <v>0.2824883504494933</v>
       </c>
       <c r="AD5">
-        <v>3904.1</v>
+        <v>4485.5</v>
       </c>
       <c r="AE5">
-        <v>9.0421122403135</v>
+        <v>8.674904983631425</v>
       </c>
       <c r="AF5">
-        <v>3913.142112240314</v>
+        <v>4494.174904983632</v>
       </c>
       <c r="AG5">
-        <v>2419.442112240314</v>
+        <v>2228.574904983632</v>
       </c>
       <c r="AH5">
-        <v>0.443946657362043</v>
+        <v>0.6435718661115457</v>
       </c>
       <c r="AI5">
-        <v>0.2539197203999785</v>
+        <v>0.3049943033952935</v>
       </c>
       <c r="AJ5">
-        <v>0.3304913730255565</v>
+        <v>0.4723984144118987</v>
       </c>
       <c r="AK5">
-        <v>0.173844939444748</v>
+        <v>0.178719567427773</v>
       </c>
       <c r="AL5">
-        <v>44.9</v>
+        <v>57.9</v>
       </c>
       <c r="AM5">
-        <v>22.5</v>
+        <v>25.3</v>
       </c>
       <c r="AN5">
-        <v>4.253295565965791</v>
+        <v>5.40766995792494</v>
       </c>
       <c r="AO5">
-        <v>20.51224944320713</v>
+        <v>9.487046632124352</v>
       </c>
       <c r="AP5">
-        <v>2.635844985554324</v>
+        <v>2.686745638761657</v>
       </c>
       <c r="AQ5">
-        <v>40.93333333333333</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>ABC arbitrage SA (ENXTPA:ABCA)</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
-        </is>
-      </c>
-      <c r="D6">
-        <v>0.06849999999999999</v>
-      </c>
-      <c r="E6">
-        <v>0.05139999999999999</v>
-      </c>
-      <c r="G6">
-        <v>0.581056466302368</v>
-      </c>
-      <c r="H6">
-        <v>0.581056466302368</v>
-      </c>
-      <c r="I6">
-        <v>0.4316939890710382</v>
-      </c>
-      <c r="J6">
-        <v>0.4316939890710382</v>
-      </c>
-      <c r="K6">
-        <v>23.7</v>
-      </c>
-      <c r="L6">
-        <v>0.4316939890710382</v>
-      </c>
-      <c r="M6">
-        <v>26.5</v>
-      </c>
-      <c r="N6">
-        <v>0.08386075949367089</v>
-      </c>
-      <c r="O6">
-        <v>1.118143459915612</v>
-      </c>
-      <c r="P6">
-        <v>26.5</v>
-      </c>
-      <c r="Q6">
-        <v>0.08386075949367089</v>
-      </c>
-      <c r="R6">
-        <v>1.118143459915612</v>
-      </c>
-      <c r="S6">
-        <v>0</v>
-      </c>
-      <c r="T6">
-        <v>0</v>
-      </c>
-      <c r="U6">
-        <v>18.4</v>
-      </c>
-      <c r="V6">
-        <v>0.05822784810126582</v>
-      </c>
-      <c r="W6">
-        <v>0.1413237924865832</v>
-      </c>
-      <c r="X6">
-        <v>0.05172532984197342</v>
-      </c>
-      <c r="Y6">
-        <v>0.08959846264460977</v>
-      </c>
-      <c r="Z6">
-        <v>0.3507538972655252</v>
-      </c>
-      <c r="AA6">
-        <v>0.1514183490927677</v>
-      </c>
-      <c r="AB6">
-        <v>0.05146953566322627</v>
-      </c>
-      <c r="AC6">
-        <v>0.09994881342954146</v>
-      </c>
-      <c r="AD6">
-        <v>5.92</v>
-      </c>
-      <c r="AE6">
-        <v>0</v>
-      </c>
-      <c r="AF6">
-        <v>5.92</v>
-      </c>
-      <c r="AG6">
-        <v>-12.48</v>
-      </c>
-      <c r="AH6">
-        <v>0.018389662027833</v>
-      </c>
-      <c r="AI6">
-        <v>0.03283052351375332</v>
-      </c>
-      <c r="AJ6">
-        <v>-0.04111755403268318</v>
-      </c>
-      <c r="AK6">
-        <v>-0.07707509881422923</v>
-      </c>
-      <c r="AL6">
-        <v>0.074</v>
-      </c>
-      <c r="AM6">
-        <v>0.074</v>
-      </c>
-      <c r="AN6">
-        <v>0.240650406504065</v>
-      </c>
-      <c r="AO6">
-        <v>320.2702702702703</v>
-      </c>
-      <c r="AP6">
-        <v>-0.5073170731707316</v>
-      </c>
-      <c r="AQ6">
-        <v>320.2702702702703</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>HiPay Group SA (ENXTPA:ALHYP)</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
-        </is>
-      </c>
-      <c r="D7">
-        <v>0.198</v>
-      </c>
-      <c r="G7">
-        <v>-0.04728571428571429</v>
-      </c>
-      <c r="H7">
-        <v>-0.04728571428571429</v>
-      </c>
-      <c r="I7">
-        <v>0.02314285714285715</v>
-      </c>
-      <c r="J7">
-        <v>0.02314285714285715</v>
-      </c>
-      <c r="K7">
-        <v>-5.34</v>
-      </c>
-      <c r="L7">
-        <v>-0.07628571428571429</v>
-      </c>
-      <c r="M7">
-        <v>-0</v>
-      </c>
-      <c r="N7">
-        <v>-0</v>
-      </c>
-      <c r="O7">
-        <v>0</v>
-      </c>
-      <c r="P7">
-        <v>-0</v>
-      </c>
-      <c r="Q7">
-        <v>-0</v>
-      </c>
-      <c r="R7">
-        <v>0</v>
-      </c>
-      <c r="S7">
-        <v>0</v>
-      </c>
-      <c r="U7">
-        <v>2.21</v>
-      </c>
-      <c r="V7">
-        <v>0.05695876288659794</v>
-      </c>
-      <c r="W7">
-        <v>-0.1927797833935018</v>
-      </c>
-      <c r="X7">
-        <v>0.0585928038107824</v>
-      </c>
-      <c r="Y7">
-        <v>-0.2513725872042842</v>
-      </c>
-      <c r="Z7">
-        <v>6.585136406396988</v>
-      </c>
-      <c r="AA7">
-        <v>0.1523988711194732</v>
-      </c>
-      <c r="AB7">
-        <v>0.05247546044312006</v>
-      </c>
-      <c r="AC7">
-        <v>0.09992341067635312</v>
-      </c>
-      <c r="AD7">
-        <v>28.6</v>
-      </c>
-      <c r="AE7">
-        <v>0</v>
-      </c>
-      <c r="AF7">
-        <v>28.6</v>
-      </c>
-      <c r="AG7">
-        <v>26.39</v>
-      </c>
-      <c r="AH7">
-        <v>0.4243323442136498</v>
-      </c>
-      <c r="AI7">
-        <v>0.5510597302504817</v>
-      </c>
-      <c r="AJ7">
-        <v>0.4048166896763307</v>
-      </c>
-      <c r="AK7">
-        <v>0.531092775206279</v>
-      </c>
-      <c r="AL7">
-        <v>1.81</v>
-      </c>
-      <c r="AM7">
-        <v>1.81</v>
-      </c>
-      <c r="AN7">
-        <v>42.6865671641791</v>
-      </c>
-      <c r="AO7">
-        <v>0.8950276243093923</v>
-      </c>
-      <c r="AP7">
-        <v>39.38805970149254</v>
-      </c>
-      <c r="AQ7">
-        <v>0.8950276243093923</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>BD Multimedia SA (ENXTPA:ALBDM)</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
-        </is>
-      </c>
-      <c r="D8">
-        <v>-0.172</v>
-      </c>
-      <c r="G8">
-        <v>-0.4375000000000001</v>
-      </c>
-      <c r="H8">
-        <v>-0.4375000000000001</v>
-      </c>
-      <c r="I8">
-        <v>-0.5125000000000001</v>
-      </c>
-      <c r="J8">
-        <v>-0.5125000000000001</v>
-      </c>
-      <c r="K8">
-        <v>-0.76</v>
-      </c>
-      <c r="L8">
-        <v>-0.3166666666666667</v>
-      </c>
-      <c r="M8">
-        <v>-0</v>
-      </c>
-      <c r="N8">
-        <v>-0</v>
-      </c>
-      <c r="O8">
-        <v>0</v>
-      </c>
-      <c r="P8">
-        <v>-0</v>
-      </c>
-      <c r="Q8">
-        <v>-0</v>
-      </c>
-      <c r="R8">
-        <v>0</v>
-      </c>
-      <c r="S8">
-        <v>0</v>
-      </c>
-      <c r="U8">
-        <v>1.11</v>
-      </c>
-      <c r="V8">
-        <v>0.3255131964809384</v>
-      </c>
-      <c r="W8">
-        <v>-0.3220338983050848</v>
-      </c>
-      <c r="X8">
-        <v>0.0532451124453517</v>
-      </c>
-      <c r="Y8">
-        <v>-0.3752790107504365</v>
-      </c>
-      <c r="Z8">
-        <v>16.00000000000002</v>
-      </c>
-      <c r="AA8">
-        <v>-8.20000000000001</v>
-      </c>
-      <c r="AB8">
-        <v>0.05187667734156189</v>
-      </c>
-      <c r="AC8">
-        <v>-8.251876677341572</v>
-      </c>
-      <c r="AD8">
-        <v>0.606</v>
-      </c>
-      <c r="AE8">
-        <v>0</v>
-      </c>
-      <c r="AF8">
-        <v>0.606</v>
-      </c>
-      <c r="AG8">
-        <v>-0.5040000000000001</v>
-      </c>
-      <c r="AH8">
-        <v>0.1508964143426295</v>
-      </c>
-      <c r="AI8">
-        <v>0.1748413156376226</v>
-      </c>
-      <c r="AJ8">
-        <v>-0.1734342739160358</v>
-      </c>
-      <c r="AK8">
-        <v>-0.2139219015280136</v>
-      </c>
-      <c r="AL8">
-        <v>0.024</v>
-      </c>
-      <c r="AM8">
-        <v>0.024</v>
-      </c>
-      <c r="AN8">
-        <v>-0.531578947368421</v>
-      </c>
-      <c r="AO8">
-        <v>-51.25</v>
-      </c>
-      <c r="AP8">
-        <v>0.4421052631578949</v>
-      </c>
-      <c r="AQ8">
-        <v>-51.25</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>CFI-Compagnie Foncière Internationale (ENXTPA:CFI)</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
-        </is>
-      </c>
-      <c r="K9">
-        <v>-0.056</v>
-      </c>
-      <c r="M9">
-        <v>-0</v>
-      </c>
-      <c r="N9">
-        <v>-0</v>
-      </c>
-      <c r="O9">
-        <v>0</v>
-      </c>
-      <c r="P9">
-        <v>-0</v>
-      </c>
-      <c r="Q9">
-        <v>-0</v>
-      </c>
-      <c r="R9">
-        <v>0</v>
-      </c>
-      <c r="S9">
-        <v>0</v>
-      </c>
-      <c r="U9">
-        <v>0</v>
-      </c>
-      <c r="V9">
-        <v>0</v>
-      </c>
-      <c r="X9">
-        <v>0.0515462371428773</v>
-      </c>
-      <c r="AB9">
-        <v>0.0515462371428773</v>
-      </c>
-      <c r="AD9">
-        <v>0</v>
-      </c>
-      <c r="AE9">
-        <v>0</v>
-      </c>
-      <c r="AF9">
-        <v>0</v>
-      </c>
-      <c r="AG9">
-        <v>0</v>
-      </c>
-      <c r="AH9">
-        <v>0</v>
-      </c>
-      <c r="AJ9">
-        <v>0</v>
-      </c>
-      <c r="AL9">
-        <v>0</v>
-      </c>
-      <c r="AM9">
-        <v>0</v>
-      </c>
-      <c r="AN9">
-        <v>-0</v>
-      </c>
-      <c r="AP9">
-        <v>-0</v>
+        <v>21.71146245059289</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/france/france_financial_svcs_non_bank_insurance.xlsx
+++ b/research/traditional_assets/database/data/france/france_financial_svcs_non_bank_insurance.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ5"/>
+  <dimension ref="A1:AQ6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,118 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.148</v>
+        <v>0.08765000000000001</v>
       </c>
       <c r="E2">
-        <v>0.0168</v>
+        <v>-0.0342</v>
       </c>
       <c r="F2">
-        <v>0.172</v>
+        <v>0.047</v>
       </c>
       <c r="G2">
-        <v>0.2615230905861456</v>
+        <v>0.2396933840447012</v>
       </c>
       <c r="H2">
-        <v>0.2309502664298402</v>
+        <v>0.1858125557590271</v>
       </c>
       <c r="I2">
-        <v>0.1723173866566689</v>
+        <v>0.1129883354078183</v>
       </c>
       <c r="J2">
-        <v>0.1254406400277555</v>
+        <v>0.1125153609805298</v>
       </c>
       <c r="K2">
-        <v>-525.1</v>
+        <v>-969.0500000000001</v>
       </c>
       <c r="L2">
-        <v>-0.05829262877442274</v>
+        <v>-0.1895904744017154</v>
       </c>
       <c r="M2">
-        <v>589.0633</v>
+        <v>19.1</v>
       </c>
       <c r="N2">
-        <v>0.04416693908766458</v>
+        <v>0.006792511878005065</v>
       </c>
       <c r="O2">
-        <v>-1.121811654922872</v>
+        <v>-0.01971002528249316</v>
       </c>
       <c r="P2">
-        <v>346.8633</v>
+        <v>19.1</v>
       </c>
       <c r="Q2">
-        <v>0.02600720541043097</v>
+        <v>0.006792511878005065</v>
       </c>
       <c r="R2">
-        <v>-0.6605661778708817</v>
+        <v>-0.01971002528249316</v>
       </c>
       <c r="S2">
-        <v>242.2</v>
+        <v>0</v>
       </c>
       <c r="T2">
-        <v>0.4111612453194758</v>
+        <v>0</v>
       </c>
       <c r="U2">
-        <v>5428.4</v>
+        <v>2278.515</v>
       </c>
       <c r="V2">
-        <v>0.4070119665297063</v>
+        <v>0.8103057697231784</v>
       </c>
       <c r="W2">
-        <v>-0.09696875060995842</v>
+        <v>0.00226103753905748</v>
       </c>
       <c r="X2">
-        <v>0.06438550124326707</v>
+        <v>0.06503836757693618</v>
       </c>
       <c r="Y2">
-        <v>-0.1613542518532255</v>
+        <v>-0.06277733003787869</v>
       </c>
       <c r="Z2">
-        <v>5.535975249133169</v>
+        <v>2.844411947024658</v>
+      </c>
+      <c r="AA2">
+        <v>0.2250854470134301</v>
       </c>
       <c r="AB2">
-        <v>0.05742288563080732</v>
+        <v>0.05784964211398563</v>
+      </c>
+      <c r="AC2">
+        <v>0.1669048613682889</v>
       </c>
       <c r="AD2">
-        <v>11265.9</v>
+        <v>4516.53</v>
       </c>
       <c r="AE2">
         <v>8.674904983631425</v>
       </c>
       <c r="AF2">
-        <v>11274.57490498363</v>
+        <v>4525.204904983631</v>
       </c>
       <c r="AG2">
-        <v>5846.174904983633</v>
+        <v>2246.689904983632</v>
       </c>
       <c r="AH2">
-        <v>0.4580967828817842</v>
+        <v>0.6167545140072448</v>
       </c>
       <c r="AI2">
-        <v>0.5362926844275527</v>
+        <v>0.3023211489760522</v>
       </c>
       <c r="AJ2">
-        <v>0.304752158258913</v>
+        <v>0.444131875591008</v>
       </c>
       <c r="AK2">
-        <v>0.3748803647762409</v>
+        <v>0.177048448134362</v>
       </c>
       <c r="AL2">
-        <v>290</v>
+        <v>59.604</v>
       </c>
       <c r="AM2">
-        <v>-77.40000000000003</v>
+        <v>25.843</v>
       </c>
       <c r="AN2">
-        <v>5.563215098737327</v>
+        <v>5.292023059077168</v>
       </c>
       <c r="AO2">
-        <v>5.334137931034483</v>
+        <v>9.599691295886181</v>
       </c>
       <c r="AP2">
-        <v>2.886900158998766</v>
+        <v>2.632448978257483</v>
       </c>
       <c r="AQ2">
-        <v>-19.98578811369508</v>
+        <v>22.14061834926286</v>
       </c>
     </row>
     <row r="3">
@@ -710,7 +716,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Edenred SE (ENXTPA:EDEN)</t>
+          <t>HiPay Group SA (ENXTPA:ALHYP)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -719,115 +725,115 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.118</v>
-      </c>
-      <c r="E3">
-        <v>0.0168</v>
-      </c>
-      <c r="F3">
-        <v>0.172</v>
+        <v>0.162</v>
       </c>
       <c r="G3">
-        <v>0.2668955480091055</v>
+        <v>0.07940379403794039</v>
       </c>
       <c r="H3">
-        <v>0.2668955480091055</v>
+        <v>0.07940379403794039</v>
       </c>
       <c r="I3">
-        <v>0.2319289472702168</v>
+        <v>0.09254742547425475</v>
       </c>
       <c r="J3">
-        <v>0.1344542220413389</v>
+        <v>0.09099779416398816</v>
       </c>
       <c r="K3">
-        <v>321.4</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="L3">
-        <v>0.1199387991193044</v>
+        <v>0.1144986449864499</v>
       </c>
       <c r="M3">
-        <v>496.1</v>
+        <v>-0</v>
       </c>
       <c r="N3">
-        <v>0.06185168561739477</v>
+        <v>-0</v>
       </c>
       <c r="O3">
-        <v>1.543559427504667</v>
+        <v>-0</v>
       </c>
       <c r="P3">
-        <v>290.4</v>
+        <v>-0</v>
       </c>
       <c r="Q3">
-        <v>0.03620586475164572</v>
+        <v>-0</v>
       </c>
       <c r="R3">
-        <v>0.9035469819539514</v>
+        <v>-0</v>
       </c>
       <c r="S3">
-        <v>205.7</v>
-      </c>
-      <c r="T3">
-        <v>0.4146341463414634</v>
+        <v>0</v>
       </c>
       <c r="U3">
-        <v>1591.1</v>
+        <v>0.195</v>
       </c>
       <c r="V3">
-        <v>0.1983717334929184</v>
+        <v>0.007442748091603054</v>
       </c>
       <c r="W3">
-        <v>-0.4440453163857419</v>
+        <v>0.3626609442060085</v>
       </c>
       <c r="X3">
-        <v>0.06438550124326707</v>
+        <v>0.06681042448244331</v>
       </c>
       <c r="Y3">
-        <v>-0.508430817629009</v>
+        <v>0.2958505197235652</v>
+      </c>
+      <c r="Z3">
+        <v>12.74611398963729</v>
+      </c>
+      <c r="AA3">
+        <v>1.159868257219744</v>
       </c>
       <c r="AB3">
-        <v>0.05689814306340023</v>
+        <v>0.05756733708555194</v>
+      </c>
+      <c r="AC3">
+        <v>1.102300920134192</v>
       </c>
       <c r="AD3">
-        <v>5474.1</v>
+        <v>24.8</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>5474.1</v>
+        <v>24.8</v>
       </c>
       <c r="AG3">
-        <v>3883</v>
+        <v>24.605</v>
       </c>
       <c r="AH3">
-        <v>0.4056421314718894</v>
+        <v>0.4862745098039216</v>
       </c>
       <c r="AI3">
-        <v>1.192588396766955</v>
+        <v>0.4404973357015986</v>
       </c>
       <c r="AJ3">
-        <v>0.3261983568272316</v>
+        <v>0.4843027261096349</v>
       </c>
       <c r="AK3">
-        <v>1.294764921640547</v>
+        <v>0.4385527136618839</v>
       </c>
       <c r="AL3">
-        <v>174.6</v>
+        <v>1.6</v>
       </c>
       <c r="AM3">
-        <v>-111.5</v>
+        <v>0.4700000000000002</v>
       </c>
       <c r="AN3">
-        <v>7.236087243886319</v>
+        <v>3.573487031700288</v>
       </c>
       <c r="AO3">
-        <v>3.559564719358534</v>
+        <v>4.26875</v>
       </c>
       <c r="AP3">
-        <v>5.132848645076009</v>
+        <v>3.545389048991354</v>
       </c>
       <c r="AQ3">
-        <v>-5.573991031390134</v>
+        <v>14.53191489361702</v>
       </c>
     </row>
     <row r="4">
@@ -838,7 +844,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Pluxee N.V. (ENXTPA:PLX)</t>
+          <t>Worldline SA (ENXTPA:WLN)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -846,110 +852,119 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="D4">
+        <v>0.178</v>
+      </c>
       <c r="F4">
-        <v>0.195</v>
+        <v>0.047</v>
       </c>
       <c r="G4">
-        <v>0.3281028170066503</v>
+        <v>0.2407815631262525</v>
       </c>
       <c r="H4">
-        <v>0.3281028170066503</v>
+        <v>0.1855911823647295</v>
       </c>
       <c r="I4">
-        <v>0.2810281700665023</v>
+        <v>0.1111493024054657</v>
       </c>
       <c r="J4">
-        <v>0.1697878527485119</v>
+        <v>0.1111493024054657</v>
       </c>
       <c r="K4">
-        <v>147.1</v>
+        <v>-993.6</v>
       </c>
       <c r="L4">
-        <v>0.109915564522155</v>
+        <v>-0.1991182364729459</v>
       </c>
       <c r="M4">
-        <v>92.9633</v>
+        <v>-0</v>
       </c>
       <c r="N4">
-        <v>0.03287942986489354</v>
+        <v>-0</v>
       </c>
       <c r="O4">
-        <v>0.6319734874235214</v>
+        <v>0</v>
       </c>
       <c r="P4">
-        <v>56.4633</v>
+        <v>-0</v>
       </c>
       <c r="Q4">
-        <v>0.019970043149183</v>
+        <v>-0</v>
       </c>
       <c r="R4">
-        <v>0.3838429639700884</v>
+        <v>0</v>
       </c>
       <c r="S4">
-        <v>36.5</v>
-      </c>
-      <c r="T4">
-        <v>0.3926280585994688</v>
+        <v>0</v>
       </c>
       <c r="U4">
-        <v>1571.7</v>
+        <v>2265.6</v>
       </c>
       <c r="V4">
-        <v>0.5558817287967744</v>
+        <v>0.9102450783447167</v>
       </c>
       <c r="W4">
-        <v>3.225877192982456</v>
+        <v>-0.09696875060995842</v>
       </c>
       <c r="X4">
-        <v>0.06235277660478426</v>
+        <v>0.07472700619733066</v>
       </c>
       <c r="Y4">
-        <v>3.163524416377672</v>
+        <v>-0.1716957568072891</v>
+      </c>
+      <c r="Z4">
+        <v>3.066664797199657</v>
+      </c>
+      <c r="AA4">
+        <v>0.3408576529201408</v>
       </c>
       <c r="AB4">
-        <v>0.05742288563080732</v>
+        <v>0.05836448516301032</v>
+      </c>
+      <c r="AC4">
+        <v>0.2824931677571304</v>
       </c>
       <c r="AD4">
-        <v>1306.3</v>
+        <v>4485.5</v>
       </c>
       <c r="AE4">
-        <v>0</v>
+        <v>8.674904983631425</v>
       </c>
       <c r="AF4">
-        <v>1306.3</v>
+        <v>4494.174904983632</v>
       </c>
       <c r="AG4">
-        <v>-265.4000000000001</v>
+        <v>2228.574904983632</v>
       </c>
       <c r="AH4">
-        <v>0.3160122892324068</v>
+        <v>0.6435718661115457</v>
       </c>
       <c r="AI4">
-        <v>0.7694074684886324</v>
+        <v>0.3049943033952935</v>
       </c>
       <c r="AJ4">
-        <v>-0.1035909445745512</v>
+        <v>0.4723984144118987</v>
       </c>
       <c r="AK4">
-        <v>-2.104678826328313</v>
+        <v>0.178719567427773</v>
       </c>
       <c r="AL4">
-        <v>57.5</v>
+        <v>57.9</v>
       </c>
       <c r="AM4">
-        <v>8.799999999999997</v>
+        <v>25.3</v>
       </c>
       <c r="AN4">
-        <v>2.974948758824869</v>
+        <v>5.40766995792494</v>
       </c>
       <c r="AO4">
-        <v>6.540869565217392</v>
+        <v>9.487046632124352</v>
       </c>
       <c r="AP4">
-        <v>-0.6044181279890687</v>
+        <v>2.686745638761657</v>
       </c>
       <c r="AQ4">
-        <v>42.73863636363638</v>
+        <v>21.71146245059289</v>
       </c>
     </row>
     <row r="5">
@@ -960,7 +975,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Worldline SA (ENXTPA:WLN)</t>
+          <t>ABC arbitrage SA (ENXTPA:ABCA)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -969,118 +984,249 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.178</v>
-      </c>
-      <c r="F5">
-        <v>0.047</v>
+        <v>0.0133</v>
+      </c>
+      <c r="E5">
+        <v>-0.0342</v>
       </c>
       <c r="G5">
-        <v>0.2407815631262525</v>
+        <v>0.420704845814978</v>
       </c>
       <c r="H5">
-        <v>0.1855911823647295</v>
+        <v>0.420704845814978</v>
       </c>
       <c r="I5">
-        <v>0.1111493024054657</v>
+        <v>0.3898678414096916</v>
       </c>
       <c r="J5">
-        <v>0.1111493024054657</v>
+        <v>0.3898678414096916</v>
       </c>
       <c r="K5">
-        <v>-993.6</v>
+        <v>17.7</v>
       </c>
       <c r="L5">
-        <v>-0.1991182364729459</v>
+        <v>0.3898678414096916</v>
       </c>
       <c r="M5">
-        <v>-0</v>
+        <v>19.1</v>
       </c>
       <c r="N5">
-        <v>-0</v>
+        <v>0.06489976214746858</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>1.07909604519774</v>
       </c>
       <c r="P5">
-        <v>-0</v>
+        <v>19.1</v>
       </c>
       <c r="Q5">
-        <v>-0</v>
+        <v>0.06489976214746858</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>1.07909604519774</v>
       </c>
       <c r="S5">
         <v>0</v>
       </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
       <c r="U5">
-        <v>2265.6</v>
+        <v>11.7</v>
       </c>
       <c r="V5">
-        <v>0.9102450783447167</v>
+        <v>0.03975535168195718</v>
       </c>
       <c r="W5">
-        <v>-0.09696875060995842</v>
+        <v>0.1014908256880734</v>
       </c>
       <c r="X5">
-        <v>0.07474052170629047</v>
+        <v>0.05823984232530096</v>
       </c>
       <c r="Y5">
-        <v>-0.1717092723162489</v>
+        <v>0.04325098336277242</v>
       </c>
       <c r="Z5">
-        <v>3.066664797199657</v>
+        <v>0.2803853754940712</v>
       </c>
       <c r="AA5">
-        <v>0.3408576529201408</v>
+        <v>0.1093132411067194</v>
       </c>
       <c r="AB5">
-        <v>0.05836930247064742</v>
+        <v>0.05799668612727205</v>
       </c>
       <c r="AC5">
-        <v>0.2824883504494933</v>
+        <v>0.05131655497944733</v>
       </c>
       <c r="AD5">
-        <v>4485.5</v>
+        <v>4.87</v>
       </c>
       <c r="AE5">
-        <v>8.674904983631425</v>
+        <v>0</v>
       </c>
       <c r="AF5">
-        <v>4494.174904983632</v>
+        <v>4.87</v>
       </c>
       <c r="AG5">
-        <v>2228.574904983632</v>
+        <v>-6.829999999999999</v>
       </c>
       <c r="AH5">
-        <v>0.6435718661115457</v>
+        <v>0.01627837015743557</v>
       </c>
       <c r="AI5">
-        <v>0.3049943033952935</v>
+        <v>0.02797725053139542</v>
       </c>
       <c r="AJ5">
-        <v>0.4723984144118987</v>
+        <v>-0.02375900093922844</v>
       </c>
       <c r="AK5">
-        <v>0.178719567427773</v>
+        <v>-0.04206442076738314</v>
       </c>
       <c r="AL5">
-        <v>57.9</v>
+        <v>0.066</v>
       </c>
       <c r="AM5">
-        <v>25.3</v>
+        <v>0.066</v>
       </c>
       <c r="AN5">
-        <v>5.40766995792494</v>
+        <v>0.2618279569892473</v>
       </c>
       <c r="AO5">
-        <v>9.487046632124352</v>
+        <v>268.1818181818181</v>
       </c>
       <c r="AP5">
-        <v>2.686745638761657</v>
+        <v>-0.3672043010752687</v>
       </c>
       <c r="AQ5">
-        <v>21.71146245059289</v>
+        <v>268.1818181818181</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>BD Multimedia SA (ENXTPA:ALBDM)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D6">
+        <v>-0.24</v>
+      </c>
+      <c r="G6">
+        <v>-0.6346153846153846</v>
+      </c>
+      <c r="H6">
+        <v>-0.6346153846153846</v>
+      </c>
+      <c r="I6">
+        <v>-0.7932692307692307</v>
+      </c>
+      <c r="J6">
+        <v>-0.7932692307692307</v>
+      </c>
+      <c r="K6">
+        <v>-1.6</v>
+      </c>
+      <c r="L6">
+        <v>-0.7692307692307693</v>
+      </c>
+      <c r="M6">
+        <v>-0</v>
+      </c>
+      <c r="N6">
+        <v>-0</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <v>-0</v>
+      </c>
+      <c r="Q6">
+        <v>-0</v>
+      </c>
+      <c r="R6">
+        <v>0</v>
+      </c>
+      <c r="S6">
+        <v>0</v>
+      </c>
+      <c r="U6">
+        <v>1.02</v>
+      </c>
+      <c r="V6">
+        <v>0.4214876033057852</v>
+      </c>
+      <c r="W6">
+        <v>-0.5614035087719298</v>
+      </c>
+      <c r="X6">
+        <v>0.06326631067142904</v>
+      </c>
+      <c r="Y6">
+        <v>-0.6246698194433589</v>
+      </c>
+      <c r="Z6">
+        <v>1.004830917874396</v>
+      </c>
+      <c r="AA6">
+        <v>-0.7971014492753622</v>
+      </c>
+      <c r="AB6">
+        <v>0.05770259810069922</v>
+      </c>
+      <c r="AC6">
+        <v>-0.8548040473760614</v>
+      </c>
+      <c r="AD6">
+        <v>1.36</v>
+      </c>
+      <c r="AE6">
+        <v>0</v>
+      </c>
+      <c r="AF6">
+        <v>1.36</v>
+      </c>
+      <c r="AG6">
+        <v>0.3400000000000001</v>
+      </c>
+      <c r="AH6">
+        <v>0.3597883597883598</v>
+      </c>
+      <c r="AI6">
+        <v>0.53125</v>
+      </c>
+      <c r="AJ6">
+        <v>0.1231884057971015</v>
+      </c>
+      <c r="AK6">
+        <v>0.2207792207792208</v>
+      </c>
+      <c r="AL6">
+        <v>0.038</v>
+      </c>
+      <c r="AM6">
+        <v>0.006999999999999999</v>
+      </c>
+      <c r="AN6">
+        <v>-0.8774193548387097</v>
+      </c>
+      <c r="AO6">
+        <v>-43.42105263157895</v>
+      </c>
+      <c r="AP6">
+        <v>-0.2193548387096775</v>
+      </c>
+      <c r="AQ6">
+        <v>-235.7142857142857</v>
       </c>
     </row>
   </sheetData>
